--- a/outputs/candidates/baseline/candidate_02_fairness.xlsx
+++ b/outputs/candidates/baseline/candidate_02_fairness.xlsx
@@ -4211,10 +4211,10 @@
         <v>1</v>
       </c>
       <c r="S2">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T2">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="U2">
         <v>34</v>
